--- a/stories/arbres/ATOM-SOC.ARG.002-07.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Roxane est à la papeterie avec papa. Elle voit un cahier. Elle a envie. L'argent se range. Roxane ne le prend pas. Elle va demander à papa. Papa, c'est l'adulte. Roxane dit : s'il te plaît, ce cahier ? Papa écoute. Il dit oui. Il paie. Roxane dit merci. On demande à l'adulte.</t>
+          <t>Roxane est à la papeterie avec papa. Elle voit un cahier. Elle a envie. L'argent se range. Roxane ne le prend pas. Elle va demander à papa. Papa, c'est l'adulte. S'il te plaît, ce cahier ? Papa écoute. Il dit oui. Il paie. Roxane dit merci. On demande à l'adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Roxane est à la papeterie avec papa. Elle voit un cahier. Elle a envie. L'argent se range. Roxane ne le prend pas. Elle va demander à papa. Papa, c'est l'adulte.
+enfant-f|S'il te plaît, ce cahier ? Papa écoute. Il dit oui. Il paie.
+narrateur|Roxane dit merci. On demande à l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Roxane veut un cahier. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Roxane a demandé à l'adulte. Papa a écouté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1824,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Ils sortent. Roxane tient le cahier.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1991,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2031,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.ARG.002-07.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Roxane dit merci. On demande à l'adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Roxane veut un cahier. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Roxane a demandé à l'adulte. Papa a écouté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1837,7 @@
           <t>narrateur|Ils sortent. Roxane tient le cahier.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1996,6 +2005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2014,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2048,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2263,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.ARG.002-07.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Roxane demande pour un cahier</t>
+          <t>Le cahier bleu de Raphaël</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël veut un cahier bleu. Il tend la main. Papa attend. Il demande. Puis il demande une gomme. Les deux sont à lui.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Roxane est à la papeterie avec papa. Elle voit un cahier. Elle a envie. L'argent se range. Roxane ne le prend pas. Elle va demander à papa. Papa, c'est l'adulte. S'il te plaît, ce cahier ? Papa écoute. Il dit oui. Il paie. Roxane dit merci. On demande à l'adulte.</t>
+          <t>Les cahiers bleus sentent l'encre froide. Ils sont empilés, bien droits. Le sol de bois craque un peu. Une pile de feuilles penche un peu. Papa pousse la porte. Une clochette fait un ding bas. Les cahiers ! Oui. On en prend un, pour dessiner. Raphaël passe près d'un bac à crayons. Les bouts pointent comme des toits. Tu as vu le bleu ? Oui. Il brille. Un cahier rouge est trop loin. Le bleu, papa. En ce moment, Raphaël touche un cahier. La couverture est lisse, d'un bleu profond. Celui-là. Il est bleu. Raphaël tire le cahier de la pile. La pile penche un peu. Papa ne sort pas l'argent. Raphaël. Tu me demandes ? Le cahier reste dans ses mains, encore. Oh. Il repose le cahier sur la pile. On achète si tu demandes. Tu te souviens ? Je peux demander. Tu me dis s'il te plaît ? Oui, papa. Le bleu attend sur le bois.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Roxane est à la papeterie avec papa. Elle voit un cahier. Elle a envie. L'argent se range. Roxane ne le prend pas. Elle va &lt;emphasis level="moderate"&gt;demander&lt;/emphasis&gt; à papa. Papa, c'est l'adulte. Roxane dit : s'il te plaît, ce cahier ? Papa écoute. Il dit oui. Il paie. Roxane dit merci. On demande à l'adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les cahiers bleus sentent l'encre froide. Ils sont empilés, bien droits. Le sol de bois craque un peu. Une pile de feuilles penche un peu. Papa pousse la porte. Une clochette fait un ding bas. Les cahiers ! Oui. On en prend un, pour dessiner. Raphaël passe près d'un bac à crayons. Les bouts pointent comme des toits. Tu as vu le bleu ? Oui. Il brille. Un cahier rouge est trop loin. Le bleu, papa. En ce moment, Raphaël touche un cahier. La couverture est lisse, d'un bleu profond. Celui-là. Il est bleu. Raphaël tire le cahier de la pile. La pile penche un peu. Papa ne sort pas l'argent. Raphaël. Tu me demandes ? Le cahier reste dans ses mains, encore. Oh. Il repose le cahier sur la pile. On achète si tu demandes. Tu te souviens ? Je peux demander. Tu me dis s'il te plaît ? Oui, papa. Le bleu attend sur le bois.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,12 +1324,42 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Roxane est à la papeterie avec papa. Elle voit un cahier. Elle a envie. L'argent se range. Roxane ne le prend pas. Elle va demander à papa. Papa, c'est l'adulte.
-enfant-f|S'il te plaît, ce cahier ? Papa écoute. Il dit oui. Il paie.
-narrateur|Roxane dit merci. On demande à l'adulte.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Les cahiers bleus sentent l'encre froide.
+narrateur|Ils sont empilés, bien droits.
+narrateur|Le sol de bois craque un peu.
+narrateur|Une pile de feuilles penche un peu.
+narrateur|Papa pousse la porte.
+narrateur|Une clochette fait un ding bas.
+enfant-m|Les cahiers !
+papa|Oui.
+papa|On en prend un, pour dessiner.
+narrateur|Raphaël passe près d'un bac à crayons.
+narrateur|Les bouts pointent comme des toits.
+papa|Tu as vu le bleu ?
+enfant-m|Oui.
+enfant-m|Il brille.
+narrateur|Un cahier rouge est trop loin.
+enfant-m|Le bleu, papa.
+narrateur|En ce moment, Raphaël touche un cahier.
+narrateur|La couverture est lisse, d'un bleu profond.
+enfant-m|Celui-là.
+enfant-m|Il est bleu.
+narrateur|Raphaël tire le cahier de la pile.
+narrateur|La pile penche un peu.
+narrateur|Papa ne sort pas l'argent.
+papa|Raphaël.
+papa|Tu me demandes ?
+narrateur|Le cahier reste dans ses mains, encore.
+enfant-m|Oh.
+narrateur|Il repose le cahier sur la pile.
+papa|On achète si tu demandes.
+papa|Tu te souviens ?
+enfant-m|Je peux demander.
+papa|Tu me dis s'il te plaît ?
+enfant-m|Oui, papa.
+narrateur|Le bleu attend sur le bois.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,19 +1384,19 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Raphaël veut le cahier bleu. Que fait-il ?</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Raphaël veut le cahier bleu. Que fait-il ?</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>Roxane veut un cahier. Que fait-elle ?</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Roxane veut un cahier. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Roxane veut un cahier. Que fait-elle ?</t>
-        </is>
-      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>demander</t>
@@ -1362,7 +1404,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>demander | papa | l'adulte</t>
+          <t>demander | il demande | à papa | s'il te plaît</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1377,7 +1419,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>L'argent se range. Elle le dit à qui ?</t>
+          <t>Il demande à papa. Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1419,14 +1461,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1498,10 +1540,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Roxane veut un cahier. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Raphaël veut le cahier bleu.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1526,12 +1568,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Roxane a demandé à l'adulte. Papa a écouté.</t>
+          <t>Papa, s'il te plaît. Je peux avoir ce cahier ? Oui. Merci, Raphaël. Tu as demandé. Papa pose l'argent sur le comptoir. On lui tend le cahier bleu. Raphaël le serre sous le bras. Plus loin, un bac tient des gommes. Une gomme blanche a roulé au bord. Papa. La gomme aussi, s'il te plaît ? Tu demandes encore. Oui. On prend la gomme. Papa ajoute une pièce. Raphaël prend la gomme. Elle est souple, un peu rêche. J'ai les deux. Parce que tu as demandé. Tu tiens bien tout ? Oui, papa. Le bac à gommes a un trou blanc.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Roxane a demandé à l'&lt;emphasis level="moderate"&gt;adulte&lt;/emphasis&gt;. Papa a écouté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa, s'il te plaît. Je peux avoir ce cahier ? Oui. Merci, Raphaël. Tu as demandé. Papa pose l'argent sur le comptoir. On lui tend le cahier bleu. Raphaël le serre sous le bras. Plus loin, un bac tient des gommes. Une gomme blanche a roulé au bord. Papa. La gomme aussi, s'il te plaît ? Tu demandes encore. Oui. On prend la gomme. Papa ajoute une pièce. Raphaël prend la gomme. Elle est souple, un peu rêche. J'ai les deux. Parce que tu as demandé. Tu tiens bien tout ? Oui, papa. Le bac à gommes a un trou blanc.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1594,7 +1636,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1670,10 +1712,31 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Roxane a demandé à l'adulte. Papa a écouté.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>enfant-m|Papa, s'il te plaît.
+enfant-m|Je peux avoir ce cahier ?
+papa|Oui.
+papa|Merci, Raphaël.
+papa|Tu as demandé.
+narrateur|Papa pose l'argent sur le comptoir.
+narrateur|On lui tend le cahier bleu.
+narrateur|Raphaël le serre sous le bras.
+narrateur|Plus loin, un bac tient des gommes.
+narrateur|Une gomme blanche a roulé au bord.
+enfant-m|Papa.
+enfant-m|La gomme aussi, s'il te plaît ?
+papa|Tu demandes encore.
+papa|Oui.
+papa|On prend la gomme.
+narrateur|Papa ajoute une pièce.
+narrateur|Raphaël prend la gomme.
+narrateur|Elle est souple, un peu rêche.
+enfant-m|J'ai les deux.
+papa|Parce que tu as demandé.
+papa|Tu tiens bien tout ?
+enfant-m|Oui, papa.
+narrateur|Le bac à gommes a un trou blanc.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1698,12 +1761,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ils sortent. Roxane tient le cahier.</t>
+          <t>Ils sortent. La clochette dingue derrière eux. Raphaël a le cahier sous le bras. La gomme est dans l'autre main. On dessinera à la maison ? Oui. Et je gommerai. Tu as demandé deux fois. Bravo. La rue sent encore le papier. Le cahier tape un peu sa hanche. La gomme reste chaude dans sa paume. Tu as les deux. Le cahier et la gomme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ils sortent. Roxane tient le cahier.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils sortent. La clochette dingue derrière eux. Raphaël a le cahier sous le bras. La gomme est dans l'autre main. On dessinera à la maison ? Oui. Et je gommerai. Tu as demandé deux fois. Bravo. La rue sent encore le papier. Le cahier tape un peu sa hanche. La gomme reste chaude dans sa paume. Tu as les deux. Le cahier et la gomme.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1766,7 +1829,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1834,10 +1897,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Ils sortent. Roxane tient le cahier.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Ils sortent.
+narrateur|La clochette dingue derrière eux.
+narrateur|Raphaël a le cahier sous le bras.
+narrateur|La gomme est dans l'autre main.
+papa|On dessinera à la maison ?
+enfant-m|Oui.
+enfant-m|Et je gommerai.
+papa|Tu as demandé deux fois.
+papa|Bravo.
+narrateur|La rue sent encore le papier.
+narrateur|Le cahier tape un peu sa hanche.
+narrateur|La gomme reste chaude dans sa paume.
+papa|Tu as les deux.
+enfant-m|Le cahier et la gomme.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1862,12 +1937,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>À la table, Raphaël ouvre le cahier. La première page est blanche, un peu rêche. Il pose la gomme à côté. Je peux dessiner. Oui. Tu as le cahier dans les mains. Raphaël pose la paume sur le bleu. Il trace un petit bateau, tout simple. La voile est bleue. Comme le cahier. La gomme sent encore le caoutchouc neuf.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>À la table, Raphaël ouvre le cahier. La première page est blanche, un peu rêche. Il pose la gomme à côté. Je peux dessiner. Oui. Tu as le cahier dans les mains. Raphaël pose la paume sur le bleu. Il trace un petit bateau, tout simple. La voile est bleue. Comme le cahier. La gomme sent encore le caoutchouc neuf.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1930,7 +2005,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2002,10 +2077,19 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|À la table, Raphaël ouvre le cahier.
+narrateur|La première page est blanche, un peu rêche.
+narrateur|Il pose la gomme à côté.
+enfant-m|Je peux dessiner.
+papa|Oui.
+papa|Tu as le cahier dans les mains.
+narrateur|Raphaël pose la paume sur le bleu.
+narrateur|Il trace un petit bateau, tout simple.
+enfant-m|La voile est bleue.
+papa|Comme le cahier.
+narrateur|La gomme sent encore le caoutchouc neuf.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2062,6 +2146,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.ARG.002-07.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>papeterie</t>
+          <t>papeterie, piles de cahiers, bac à gommes</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Roxane, papa</t>
+          <t>Raphaël, papa</t>
         </is>
       </c>
     </row>
